--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\nomiya-app-test\tests\e2e\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{056C0625-9FC0-4804-BE48-AC67DC7050FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88267333-94EA-4CA8-A880-37F6F5DE79C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="21585" windowHeight="11415" xr2:uid="{BB81B485-2935-4416-8059-03D4EA08352D}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="21585" windowHeight="11415" xr2:uid="{869DF64E-7351-4259-9183-3E745E5D81F0}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -335,7 +335,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97953724-A41D-0CF5-85ED-A485C5D28666}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{321210ED-7324-5DBD-A7A2-A99C0801B921}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -686,7 +686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2867BC1B-0D47-416D-A2E7-453262011086}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F22728E-B529-4005-9940-926F7D247BFB}">
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
@@ -790,14 +790,14 @@
         <v>30909.090909090908</v>
       </c>
       <c r="F11" s="11">
+        <f>E11*0.1</f>
         <v>3090.909090909091</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
+      <c r="E12" s="12"/>
       <c r="F12" s="12">
+        <f t="shared" ref="F12:F26" si="0">E12*0.1</f>
         <v>0</v>
       </c>
     </row>
@@ -807,59 +807,107 @@
         <v>0</v>
       </c>
       <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="C14" s="10">
+        <v>0</v>
+      </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="F21" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="F23" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="F25" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A27" t="s">

--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\nomiya-app-test\tests\e2e\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88267333-94EA-4CA8-A880-37F6F5DE79C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC0BDFAA-2B41-4440-9AE2-5CD28C2893F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="21585" windowHeight="11415" xr2:uid="{869DF64E-7351-4259-9183-3E745E5D81F0}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="21585" windowHeight="11415" xr2:uid="{83C88C93-2A25-4EF4-87A1-3BF78F8C552F}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>請求書</t>
     <rPh sb="0" eb="3">
@@ -63,6 +63,18 @@
       <t>ガイシャ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>〒000-0000</t>
+  </si>
+  <si>
+    <t>○○県○○市中央7-3-40　00コーポ1号</t>
+  </si>
+  <si>
+    <t>TEL000-0000-0000</t>
+  </si>
+  <si>
+    <t>登録番号：T0000000000000</t>
   </si>
   <si>
     <t>消費税は10%となっております。</t>
@@ -258,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -276,6 +288,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -335,7 +350,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{321210ED-7324-5DBD-A7A2-A99C0801B921}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E764222-67FD-9098-8CF6-540AD61AD952}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -686,7 +701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F22728E-B529-4005-9940-926F7D247BFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E22655F-5945-483B-9E5B-E7EE917240FB}">
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
@@ -722,7 +737,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="I3" t="s">
+      <c r="I3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -731,72 +746,86 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
+      <c r="I4" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="I5" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="6" t="s">
-        <v>5</v>
+      <c r="A8" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>34000</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="D10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="11">
+        <v>17</v>
+      </c>
+      <c r="E11" s="12">
         <v>30909.090909090908</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>E11*0.1</f>
         <v>3090.909090909091</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E12" s="12"/>
-      <c r="F12" s="12">
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E12" s="13"/>
+      <c r="F12" s="13">
         <f t="shared" ref="F12:F26" si="0">E12*0.1</f>
         <v>0</v>
       </c>
@@ -806,18 +835,18 @@
         <f>C11-C11</f>
         <v>0</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="C14" s="10">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12">
+      <c r="E13" s="12"/>
+      <c r="F13" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -826,118 +855,118 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E16" s="12"/>
-      <c r="F16" s="12">
+      <c r="E15" s="12"/>
+      <c r="F15" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E16" s="13"/>
+      <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E17" s="11"/>
-      <c r="F17" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E18" s="12"/>
-      <c r="F18" s="12">
+      <c r="E17" s="12"/>
+      <c r="F17" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E18" s="13"/>
+      <c r="F18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E19" s="11"/>
-      <c r="F19" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E20" s="12"/>
-      <c r="F20" s="12">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E20" s="13"/>
+      <c r="F20" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E21" s="11"/>
-      <c r="F21" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E22" s="12"/>
-      <c r="F22" s="12">
+      <c r="E21" s="12"/>
+      <c r="F21" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E23" s="11"/>
-      <c r="F23" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E24" s="12"/>
-      <c r="F24" s="12">
+      <c r="E23" s="12"/>
+      <c r="F23" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E24" s="13"/>
+      <c r="F24" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E25" s="11"/>
-      <c r="F25" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E26" s="12"/>
-      <c r="F26" s="12">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E26" s="13"/>
+      <c r="F26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="11">
+        <v>18</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="12">
         <f>E11</f>
         <v>30909.090909090908</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" s="11">
+        <v>19</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="12">
         <f>F11</f>
         <v>3090.909090909091</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.7">
-      <c r="H29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="11">
+      <c r="H29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="12">
         <f>I27+I28</f>
         <v>34000</v>
       </c>
